--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487531_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487531_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3902</v>
+        <v>8.550599999999999</v>
       </c>
       <c r="E2" t="n">
         <v>9.1584</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7682</v>
+        <v>-0.6078</v>
       </c>
       <c r="G2" t="n">
         <v>6.8374</v>
@@ -610,13 +610,13 @@
         <v>3.3294</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0923</v>
+        <v>-0.9319</v>
       </c>
       <c r="T2" t="n">
         <v>-0.1623</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.93</v>
+        <v>-0.7696</v>
       </c>
       <c r="V2" t="n">
         <v>1.2742</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3678</v>
+        <v>1.3143</v>
       </c>
       <c r="E3" t="n">
         <v>1.8744</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.5601</v>
       </c>
       <c r="G3" t="n">
         <v>2.539</v>
@@ -688,13 +688,13 @@
         <v>0.5875</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2668</v>
+        <v>-0.3202</v>
       </c>
       <c r="T3" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.148</v>
+        <v>-0.2014</v>
       </c>
       <c r="V3" t="n">
         <v>-1.492</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>M. GONZALEZ BLAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2692</v>
+        <v>-0.254</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.07539999999999999</v>
+        <v>1.8213</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1937</v>
+        <v>-2.0754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2344</v>
+        <v>1.1037</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6952</v>
+        <v>0.3406</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9295</v>
+        <v>0.7631</v>
       </c>
       <c r="J4" t="n">
-        <v>1.099</v>
+        <v>6.0889</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3214</v>
+        <v>3.331</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7775</v>
+        <v>2.7579</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8646</v>
+        <v>-4.9852</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0166</v>
+        <v>-2.9904</v>
       </c>
       <c r="O4" t="n">
-        <v>0.152</v>
+        <v>-1.9948</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7626</v>
+        <v>3.3294</v>
       </c>
       <c r="S4" t="n">
-        <v>0.243</v>
+        <v>-0.7702</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5087</v>
+        <v>-0.3505</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2657</v>
+        <v>-0.4196</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8260999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BLAS</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1216</v>
+        <v>-0.5716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9003</v>
+        <v>-0.4848</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0219</v>
+        <v>-0.0868</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1037</v>
+        <v>0.2344</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3406</v>
+        <v>-0.6952</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7631</v>
+        <v>0.9295</v>
       </c>
       <c r="J5" t="n">
-        <v>6.0889</v>
+        <v>1.099</v>
       </c>
       <c r="K5" t="n">
-        <v>3.331</v>
+        <v>0.3214</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7579</v>
+        <v>0.7775</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.9852</v>
+        <v>-0.8646</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.9904</v>
+        <v>-1.0166</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.9948</v>
+        <v>0.152</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3294</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6377</v>
+        <v>-0.0594</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2716</v>
+        <v>0.0994</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3662</v>
+        <v>-0.1588</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4073</v>
+        <v>-1.1713</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1244</v>
+        <v>0.2267</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5317</v>
+        <v>-1.398</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2728</v>
@@ -922,13 +922,13 @@
         <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6414</v>
+        <v>-0.4054</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2682</v>
+        <v>-0.1659</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3732</v>
+        <v>-0.2395</v>
       </c>
       <c r="V6" t="n">
         <v>0.7235</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6323</v>
+        <v>-1.6545</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8868</v>
+        <v>0.7845</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5192</v>
+        <v>-2.439</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8566</v>
@@ -1000,13 +1000,13 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.267</v>
+        <v>0.2448</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3258</v>
+        <v>0.2235</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0589</v>
+        <v>0.0213</v>
       </c>
       <c r="V7" t="n">
         <v>-1.4344</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5731</v>
+        <v>-1.9812</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2417</v>
+        <v>-1.7301</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3314</v>
+        <v>-0.2512</v>
       </c>
       <c r="G8" t="n">
         <v>1.8972</v>
@@ -1078,13 +1078,13 @@
         <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9611</v>
+        <v>-0.3692</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.3023</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1471</v>
+        <v>-0.0669</v>
       </c>
       <c r="V8" t="n">
         <v>-1.159</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>M. JUAN SEVILLANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3687</v>
+        <v>-3.8762</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5681</v>
+        <v>-1.3702</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8007</v>
+        <v>-2.506</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.3087</v>
+        <v>-1.3444</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.47</v>
+        <v>-2.9762</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8387</v>
+        <v>1.6318</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4828</v>
+        <v>0.8159</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.043</v>
+        <v>-0.5275</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4397</v>
+        <v>1.3433</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.8259</v>
+        <v>-2.1603</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.427</v>
+        <v>-2.4488</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.399</v>
+        <v>0.2885</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>1.94</v>
+        <v>-0.2564</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8732</v>
+        <v>-0.2276</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0668</v>
+        <v>-0.0288</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. JUAN SEVILLANO</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9694</v>
+        <v>-4.3211</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6772</v>
+        <v>-2.3867</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2921</v>
+        <v>-1.9343</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3444</v>
+        <v>-5.3087</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.9762</v>
+        <v>-2.47</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6318</v>
+        <v>-2.8387</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8159</v>
+        <v>-1.4828</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5275</v>
+        <v>-1.043</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3433</v>
+        <v>-0.4397</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1603</v>
+        <v>-3.8259</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.4488</v>
+        <v>-1.427</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2885</v>
+        <v>-2.399</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3496</v>
+        <v>0.9876</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5346</v>
+        <v>1.0545</v>
       </c>
       <c r="U10" t="n">
-        <v>0.185</v>
+        <v>-0.0669</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7919</v>
+        <v>-6.4105</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9525</v>
+        <v>-5.4642</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8394</v>
+        <v>-0.9463</v>
       </c>
       <c r="G11" t="n">
         <v>-3.584</v>
@@ -1312,13 +1312,13 @@
         <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9256</v>
+        <v>0.307</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1027</v>
+        <v>0.5911</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1771</v>
+        <v>-0.2841</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>-10.3755</v>
       </c>
       <c r="E12" t="n">
-        <v>2.429399999999999</v>
+        <v>2.4293</v>
       </c>
       <c r="F12" t="n">
         <v>-12.8049</v>
@@ -1393,10 +1393,10 @@
         <v>-1.5733</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6409</v>
+        <v>0.6410999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2144</v>
+        <v>-2.2143</v>
       </c>
       <c r="V12" t="n">
         <v>-4.1304</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3416</v>
+        <v>4.7851</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4869</v>
+        <v>3.7939</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8547</v>
+        <v>0.9912</v>
       </c>
       <c r="G13" t="n">
         <v>2.7154</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.724</v>
+        <v>-0.2805</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4993</v>
+        <v>-0.1923</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2247</v>
+        <v>-0.0882</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3091</v>
+        <v>3.885</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2123</v>
+        <v>3.5983</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0968</v>
+        <v>0.2868</v>
       </c>
       <c r="G14" t="n">
         <v>0.5765</v>
@@ -1546,13 +1546,13 @@
         <v>2.7419</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9908</v>
+        <v>0.5667</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8828</v>
+        <v>0.2688</v>
       </c>
       <c r="U14" t="n">
-        <v>0.108</v>
+        <v>0.2979</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3688</v>
+        <v>3.1284</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2448</v>
+        <v>4.6541</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.876</v>
+        <v>-1.5257</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3434</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3085</v>
+        <v>0.4511</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0465</v>
+        <v>0.4558</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.355</v>
+        <v>-0.0047</v>
       </c>
       <c r="V15" t="n">
         <v>2.4332</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2388</v>
+        <v>3.0787</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2913</v>
+        <v>1.7007</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9475</v>
+        <v>1.378</v>
       </c>
       <c r="G16" t="n">
         <v>1.6906</v>
@@ -1702,13 +1702,13 @@
         <v>2.7419</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7479</v>
+        <v>0.0919</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4223</v>
+        <v>-0.0129</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3256</v>
+        <v>0.1048</v>
       </c>
       <c r="V16" t="n">
         <v>1.492</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6228</v>
+        <v>0.6615</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1579</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>2.7083</v>
@@ -1780,13 +1780,13 @@
         <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4392</v>
+        <v>-0.4005</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1476</v>
+        <v>-0.0571</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5868</v>
+        <v>-0.3435</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2754</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1405</v>
+        <v>0.372</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3339</v>
+        <v>1.5024</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1933</v>
+        <v>-1.1304</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8172</v>
+        <v>-0.2664</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4331</v>
+        <v>0.275</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3841</v>
+        <v>-0.5413</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7327</v>
+        <v>2.4169</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0408</v>
+        <v>0.8166</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6919</v>
+        <v>1.6003</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5499</v>
+        <v>-2.6833</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4739</v>
+        <v>-0.5416</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.076</v>
+        <v>-2.1416</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0949</v>
+        <v>0.3042</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3258</v>
+        <v>0.1223</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.231</v>
+        <v>0.1819</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2754</v>
+        <v>-0.0576</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2754</v>
+        <v>-0.0576</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0428</v>
+        <v>0.3277</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4215</v>
+        <v>0.6262</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3787</v>
+        <v>-0.2985</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2241</v>
@@ -1936,13 +1936,13 @@
         <v>0.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5164</v>
+        <v>-0.2316</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1606</v>
+        <v>0.0441</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3559</v>
+        <v>-0.2757</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3562</v>
+        <v>0.0649</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7264</v>
+        <v>1.2316</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3701</v>
+        <v>-1.1666</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0442</v>
+        <v>-0.8172</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6933</v>
+        <v>-0.4331</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.7375</v>
+        <v>-0.3841</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9797</v>
+        <v>0.7327</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7776</v>
+        <v>0.0408</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2021</v>
+        <v>0.6919</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.0238</v>
+        <v>-1.5499</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0843</v>
+        <v>-0.4739</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.9395</v>
+        <v>-1.076</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5875</v>
+        <v>0.5875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.3294</v>
+        <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>3.0565</v>
+        <v>0.0193</v>
       </c>
       <c r="T20" t="n">
-        <v>1.992</v>
+        <v>0.2235</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0645</v>
+        <v>-0.2042</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7811</v>
+        <v>0.2754</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7811</v>
+        <v>0.2754</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.7234</v>
       </c>
       <c r="E21" t="n">
-        <v>0.786</v>
+        <v>-0.7348</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3471</v>
+        <v>0.0114</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2664</v>
+        <v>-1.6285</v>
       </c>
       <c r="H21" t="n">
-        <v>0.275</v>
+        <v>0.4835</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5413</v>
+        <v>-2.112</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4169</v>
+        <v>0.8517</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8166</v>
+        <v>2.0448</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6003</v>
+        <v>-1.1932</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6833</v>
+        <v>-2.4801</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5416</v>
+        <v>-1.5613</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1416</v>
+        <v>-0.9188</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3709</v>
+        <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6288</v>
+        <v>0.1573</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.594</v>
+        <v>-0.0635</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0348</v>
+        <v>0.2209</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.0576</v>
+        <v>0.1602</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0576</v>
+        <v>0.4355</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0306</v>
+        <v>-1.8801</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6774</v>
+        <v>-1.8521</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6468</v>
+        <v>-0.028</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6122</v>
+        <v>-2.0442</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3085</v>
+        <v>0.6933</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3037</v>
+        <v>-2.7375</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1826</v>
+        <v>1.9797</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5189</v>
+        <v>1.7776</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7015</v>
+        <v>0.2021</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7948</v>
+        <v>-4.0238</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2104</v>
+        <v>-1.0843</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0052</v>
+        <v>-2.9395</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9585</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.917</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9585</v>
+        <v>3.3294</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6564</v>
+        <v>1.5327</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1733</v>
+        <v>0.8663</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4831</v>
+        <v>0.6664</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8837</v>
+        <v>-0.7811</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8837</v>
+        <v>-0.7811</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7412</v>
+        <v>-1.9598</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3488</v>
+        <v>-2.2914</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3924</v>
+        <v>0.3316</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6285</v>
+        <v>-1.6122</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4835</v>
+        <v>-0.3085</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.112</v>
+        <v>-1.3037</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8517</v>
+        <v>0.1826</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0448</v>
+        <v>-0.5189</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1932</v>
+        <v>0.7015</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4801</v>
+        <v>-1.7948</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5613</v>
+        <v>0.2104</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9188</v>
+        <v>-2.0052</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5875</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R23" t="n">
-        <v>2.546</v>
+        <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8604000000000001</v>
+        <v>0.7272</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6775</v>
+        <v>0.5593</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1829</v>
+        <v>0.1679</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1602</v>
+        <v>0.8837</v>
       </c>
       <c r="W23" t="n">
-        <v>0.4355</v>
+        <v>0.8837</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.3754</v>
+        <v>11.74</v>
       </c>
       <c r="E24" t="n">
-        <v>12.8048</v>
+        <v>12.8049</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4295</v>
+        <v>-1.0647</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7547999999999997</v>
+        <v>0.7547999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>8.181699999999998</v>
+        <v>8.181699999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-7.426699999999999</v>
@@ -2317,7 +2317,7 @@
         <v>-16.0103</v>
       </c>
       <c r="P24" t="n">
-        <v>3.917</v>
+        <v>3.917000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-17.6263</v>
@@ -2326,19 +2326,19 @@
         <v>21.5433</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5734</v>
+        <v>2.9378</v>
       </c>
       <c r="T24" t="n">
         <v>2.2143</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6411</v>
+        <v>0.7235</v>
       </c>
       <c r="V24" t="n">
         <v>4.1304</v>
       </c>
       <c r="W24" t="n">
-        <v>4.3482</v>
+        <v>4.348199999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-0.2179</v>
